--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.14618800412887</v>
+        <v>1.973755550670941</v>
       </c>
       <c r="D2" t="n">
-        <v>66.4042827837324</v>
+        <v>10.79069595235651</v>
       </c>
       <c r="E2" t="n">
-        <v>7.723689880348293</v>
+        <v>1.255099605556598</v>
       </c>
       <c r="F2" t="n">
-        <v>4.058110994479111</v>
+        <v>0.6594430366028557</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.53111765622213</v>
+        <v>3.173806619136097</v>
       </c>
       <c r="D3" t="n">
-        <v>63.23966764569543</v>
+        <v>10.27644599242551</v>
       </c>
       <c r="E3" t="n">
-        <v>7.723689880348293</v>
+        <v>1.255099605556598</v>
       </c>
       <c r="F3" t="n">
-        <v>4.058110994479111</v>
+        <v>0.6594430366028557</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.92329219213245</v>
+        <v>5.025034981221524</v>
       </c>
       <c r="D4" t="n">
-        <v>72.98261857580289</v>
+        <v>11.85967551856797</v>
       </c>
       <c r="E4" t="n">
-        <v>7.723689880348293</v>
+        <v>1.255099605556598</v>
       </c>
       <c r="F4" t="n">
-        <v>4.058110994479111</v>
+        <v>0.6594430366028557</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
